--- a/artfynd/A 12522-2020 artfynd.xlsx
+++ b/artfynd/A 12522-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12522-2020 artfynd.xlsx
+++ b/artfynd/A 12522-2020 artfynd.xlsx
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119714577</v>
+        <v>119714556</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792417</v>
+        <v>792419</v>
       </c>
       <c r="R21" t="n">
-        <v>7354468</v>
+        <v>7354475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119714556</v>
+        <v>119714577</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>792419</v>
+        <v>792417</v>
       </c>
       <c r="R22" t="n">
-        <v>7354475</v>
+        <v>7354468</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 12522-2020 artfynd.xlsx
+++ b/artfynd/A 12522-2020 artfynd.xlsx
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119714556</v>
+        <v>119714577</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792419</v>
+        <v>792417</v>
       </c>
       <c r="R21" t="n">
-        <v>7354475</v>
+        <v>7354468</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119714577</v>
+        <v>119714556</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>792417</v>
+        <v>792419</v>
       </c>
       <c r="R22" t="n">
-        <v>7354468</v>
+        <v>7354475</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 12522-2020 artfynd.xlsx
+++ b/artfynd/A 12522-2020 artfynd.xlsx
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119714577</v>
+        <v>119714556</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792417</v>
+        <v>792419</v>
       </c>
       <c r="R21" t="n">
-        <v>7354468</v>
+        <v>7354475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119714556</v>
+        <v>119714577</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,25 +2921,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>792419</v>
+        <v>792417</v>
       </c>
       <c r="R22" t="n">
-        <v>7354475</v>
+        <v>7354468</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
